--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_PROBASKETLAB FUENLABRADA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_PROBASKETLAB FUENLABRADA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. DEL CERRO RUIZ</t>
+          <t>P. RODRIGUEZ PASCUAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>30.4541</v>
+        <v>29.0651</v>
       </c>
       <c r="E2" t="n">
-        <v>11.1782</v>
+        <v>27.04</v>
       </c>
       <c r="F2" t="n">
-        <v>19.2762</v>
+        <v>2.025000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>10.1753</v>
+        <v>57.1121</v>
       </c>
       <c r="H2" t="n">
-        <v>10.5787</v>
+        <v>36.5326</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4036000000000002</v>
+        <v>20.5793</v>
       </c>
       <c r="J2" t="n">
-        <v>30.2081</v>
+        <v>86.1835</v>
       </c>
       <c r="K2" t="n">
-        <v>27.0853</v>
+        <v>57.8006</v>
       </c>
       <c r="L2" t="n">
-        <v>3.123</v>
+        <v>28.3832</v>
       </c>
       <c r="M2" t="n">
-        <v>-20.0328</v>
+        <v>-29.0716</v>
       </c>
       <c r="N2" t="n">
-        <v>-16.5065</v>
+        <v>-21.2673</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.5266</v>
+        <v>-7.803599999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>16.0256</v>
+        <v>-24.9071</v>
       </c>
       <c r="Q2" t="n">
-        <v>-40.9328</v>
+        <v>-86.69240000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>56.9581</v>
+        <v>61.7849</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2846</v>
+        <v>-19.3415</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2278</v>
+        <v>-11.3838</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.5128</v>
+        <v>-7.9577</v>
       </c>
       <c r="V2" t="n">
-        <v>4.5381</v>
+        <v>16.2014</v>
       </c>
       <c r="W2" t="n">
-        <v>20.6748</v>
+        <v>38.9324</v>
       </c>
       <c r="X2" t="n">
-        <v>-16.1363</v>
+        <v>-22.731</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>D. DEL CERRO RUIZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>26.6989</v>
+        <v>22.983</v>
       </c>
       <c r="E3" t="n">
-        <v>9.7622</v>
+        <v>4.607900000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>16.9363</v>
+        <v>18.3756</v>
       </c>
       <c r="G3" t="n">
-        <v>11.3623</v>
+        <v>10.1753</v>
       </c>
       <c r="H3" t="n">
-        <v>20.4138</v>
+        <v>10.5787</v>
       </c>
       <c r="I3" t="n">
-        <v>-9.051600000000001</v>
+        <v>-0.4036000000000002</v>
       </c>
       <c r="J3" t="n">
-        <v>35.454</v>
+        <v>30.2081</v>
       </c>
       <c r="K3" t="n">
-        <v>33.3972</v>
+        <v>27.0853</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0565</v>
+        <v>3.123</v>
       </c>
       <c r="M3" t="n">
-        <v>-24.0916</v>
+        <v>-20.0328</v>
       </c>
       <c r="N3" t="n">
-        <v>-12.9834</v>
+        <v>-16.5065</v>
       </c>
       <c r="O3" t="n">
-        <v>-11.1081</v>
+        <v>-3.5266</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9308</v>
+        <v>16.0256</v>
       </c>
       <c r="Q3" t="n">
-        <v>-41.8983</v>
+        <v>-40.9328</v>
       </c>
       <c r="R3" t="n">
-        <v>43.8285</v>
+        <v>56.9581</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1178999999999997</v>
+        <v>-7.7559</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5269</v>
+        <v>-5.3425</v>
       </c>
       <c r="U3" t="n">
-        <v>1.644599999999999</v>
+        <v>-2.4134</v>
       </c>
       <c r="V3" t="n">
-        <v>13.2881</v>
+        <v>4.5381</v>
       </c>
       <c r="W3" t="n">
-        <v>17.733</v>
+        <v>20.6748</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.4453</v>
+        <v>-16.1363</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. SOW</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>16.8182</v>
+        <v>22.1895</v>
       </c>
       <c r="E4" t="n">
-        <v>9.036300000000001</v>
+        <v>8.045899999999998</v>
       </c>
       <c r="F4" t="n">
-        <v>7.781499999999999</v>
+        <v>14.1437</v>
       </c>
       <c r="G4" t="n">
-        <v>4.355</v>
+        <v>11.3623</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9793</v>
+        <v>20.4138</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3757</v>
+        <v>-9.051600000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>4.355499999999999</v>
+        <v>35.454</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7764</v>
+        <v>33.3972</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5790000000000002</v>
+        <v>2.0565</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.000400000000000067</v>
+        <v>-24.0916</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7973</v>
+        <v>-12.9834</v>
       </c>
       <c r="O4" t="n">
-        <v>1.797</v>
+        <v>-11.1081</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1583</v>
+        <v>1.9308</v>
       </c>
       <c r="Q4" t="n">
-        <v>-11.971</v>
+        <v>-41.8983</v>
       </c>
       <c r="R4" t="n">
-        <v>10.8124</v>
+        <v>43.8285</v>
       </c>
       <c r="S4" t="n">
-        <v>7.315</v>
+        <v>-4.391400000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>4.2171</v>
+        <v>-3.2435</v>
       </c>
       <c r="U4" t="n">
-        <v>3.098</v>
+        <v>-1.1481</v>
       </c>
       <c r="V4" t="n">
-        <v>6.3063</v>
+        <v>13.2881</v>
       </c>
       <c r="W4" t="n">
-        <v>12.4348</v>
+        <v>17.733</v>
       </c>
       <c r="X4" t="n">
-        <v>-6.1282</v>
+        <v>-4.4453</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ PASCUAL</t>
+          <t>B. SOW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>10.2393</v>
+        <v>13.7165</v>
       </c>
       <c r="E5" t="n">
-        <v>15.2428</v>
+        <v>6.5753</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.0034</v>
+        <v>7.141300000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>57.1121</v>
+        <v>4.355</v>
       </c>
       <c r="H5" t="n">
-        <v>36.5326</v>
+        <v>1.9793</v>
       </c>
       <c r="I5" t="n">
-        <v>20.5793</v>
+        <v>2.3757</v>
       </c>
       <c r="J5" t="n">
-        <v>86.1835</v>
+        <v>4.355499999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>57.8006</v>
+        <v>3.7764</v>
       </c>
       <c r="L5" t="n">
-        <v>28.3832</v>
+        <v>0.5790000000000002</v>
       </c>
       <c r="M5" t="n">
-        <v>-29.0716</v>
+        <v>-0.000400000000000067</v>
       </c>
       <c r="N5" t="n">
-        <v>-21.2673</v>
+        <v>-1.7973</v>
       </c>
       <c r="O5" t="n">
-        <v>-7.803599999999999</v>
+        <v>1.797</v>
       </c>
       <c r="P5" t="n">
-        <v>-24.9071</v>
+        <v>-1.1583</v>
       </c>
       <c r="Q5" t="n">
-        <v>-86.69240000000001</v>
+        <v>-11.971</v>
       </c>
       <c r="R5" t="n">
-        <v>61.7849</v>
+        <v>10.8124</v>
       </c>
       <c r="S5" t="n">
-        <v>-38.1671</v>
+        <v>4.2135</v>
       </c>
       <c r="T5" t="n">
-        <v>-23.1811</v>
+        <v>1.756</v>
       </c>
       <c r="U5" t="n">
-        <v>-14.9861</v>
+        <v>2.4577</v>
       </c>
       <c r="V5" t="n">
-        <v>16.2014</v>
+        <v>6.3063</v>
       </c>
       <c r="W5" t="n">
-        <v>38.9324</v>
+        <v>12.4348</v>
       </c>
       <c r="X5" t="n">
-        <v>-22.731</v>
+        <v>-6.1282</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>4.9817</v>
+        <v>6.7013</v>
       </c>
       <c r="E6" t="n">
-        <v>7.8337</v>
+        <v>8.6128</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.8519</v>
+        <v>-1.9115</v>
       </c>
       <c r="G6" t="n">
         <v>8.222199999999999</v>
@@ -922,13 +922,13 @@
         <v>6.950900000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.409</v>
+        <v>-1.6895</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1043</v>
+        <v>-0.3254</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.3047</v>
+        <v>-1.3642</v>
       </c>
       <c r="V6" t="n">
         <v>-3.886</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GOMEZ FRAILE</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>1.221</v>
+        <v>5.1342</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4195</v>
+        <v>-0.3308000000000009</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1984</v>
+        <v>5.464899999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1980000000000002</v>
+        <v>-5.495299999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4551999999999998</v>
+        <v>-2.935</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6532</v>
+        <v>-2.5604</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1441</v>
+        <v>19.9107</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0627</v>
+        <v>14.7444</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0814</v>
+        <v>5.166300000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9460999999999999</v>
+        <v>-25.4062</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5179</v>
+        <v>-17.6795</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5719000000000001</v>
+        <v>-7.7266</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5446</v>
+        <v>22.59</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-34.3683</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5446</v>
+        <v>56.9578</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04960000000000001</v>
+        <v>-12.9689</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2754</v>
+        <v>-8.858599999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2257</v>
+        <v>-4.1099</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5712</v>
+        <v>1.0085</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>22.985</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5712</v>
+        <v>-21.9763</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2025</v>
+        <v>1.5046</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6807</v>
+        <v>1.7842</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4783</v>
+        <v>-0.2796</v>
       </c>
       <c r="G8" t="n">
         <v>0.4499000000000002</v>
@@ -1078,13 +1078,13 @@
         <v>2.1239</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1436</v>
+        <v>0.1585</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.05559999999999998</v>
+        <v>0.0479</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.08799999999999999</v>
+        <v>0.1106</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2277</v>
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>1.073</v>
+        <v>1.364</v>
       </c>
       <c r="E9" t="n">
-        <v>0.454</v>
+        <v>0.8195</v>
       </c>
       <c r="F9" t="n">
-        <v>0.619</v>
+        <v>0.5445</v>
       </c>
       <c r="G9" t="n">
         <v>-0.429</v>
@@ -1156,13 +1156,13 @@
         <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2703</v>
+        <v>0.0206</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2759</v>
+        <v>0.0895</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0056</v>
+        <v>-0.0689</v>
       </c>
       <c r="V9" t="n">
         <v>0.6138</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. DÍAZ HERMIDA</t>
+          <t>A. GOMEZ FRAILE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0468</v>
+        <v>0.7094</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.9574999999999998</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4567</v>
+        <v>-0.2481</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1313</v>
+        <v>0.1980000000000002</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0002</v>
+        <v>-0.4551999999999998</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1311</v>
+        <v>0.6532</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.1441</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1.0627</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.0814</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1313</v>
+        <v>-0.9460999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0002</v>
+        <v>-1.5179</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1311</v>
+        <v>0.5719000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1931</v>
+        <v>1.5446</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1931</v>
+        <v>1.5446</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6288</v>
+        <v>-0.4619</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1104</v>
+        <v>-0.1866</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5185</v>
+        <v>-0.2754</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6138</v>
+        <v>-0.5712</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Á. AGUILERA MUÑOZ</t>
+          <t>M. DÍAZ HERMIDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4103</v>
+        <v>0.1999</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9031</v>
+        <v>0.6069</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5071</v>
+        <v>-0.407</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.4002</v>
+        <v>-0.1313</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.441</v>
+        <v>-0.0002</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.9592</v>
+        <v>-0.1311</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.0549</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.7167</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3383</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3453</v>
+        <v>-0.1313</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2756</v>
+        <v>-0.0002</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.6209</v>
+        <v>-0.1311</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5792</v>
+        <v>0.1931</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1103</v>
+        <v>-0.4758</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4966</v>
+        <v>-0.0069</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3863</v>
+        <v>-0.4688</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6795</v>
+        <v>0.6138</v>
       </c>
       <c r="W11" t="n">
         <v>0.6138</v>
       </c>
       <c r="X11" t="n">
-        <v>0.06560000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4873</v>
+        <v>-1.839399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.635000000000001</v>
+        <v>-6.3872</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1475</v>
+        <v>4.547800000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-9.232799999999999</v>
@@ -1390,13 +1390,13 @@
         <v>18.5354</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.517499999999999</v>
+        <v>-1.8691</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.9833</v>
+        <v>-1.7354</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.534</v>
+        <v>-0.1337999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-2.9012</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. GUIJARRO TOMAS</t>
+          <t>Á. AGUILERA MUÑOZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,67 +1420,67 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.4969</v>
+        <v>-4.3276</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.552099999999999</v>
+        <v>-3.6963</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05519999999999999</v>
+        <v>-0.6313</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.7878</v>
+        <v>-4.4002</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.7381</v>
+        <v>-1.441</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.04969999999999997</v>
+        <v>-2.9592</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.9315</v>
+        <v>-3.0549</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.6339</v>
+        <v>-1.7167</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2976</v>
+        <v>-1.3383</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1436999999999999</v>
+        <v>-1.3453</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1041</v>
+        <v>0.2756</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2479</v>
+        <v>-1.6209</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1584</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7724</v>
+        <v>0.3862</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6164</v>
+        <v>-0.0276</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6898000000000001</v>
+        <v>-0.2898</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9265000000000001</v>
+        <v>0.2622</v>
       </c>
       <c r="V13" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.6795</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X13" t="n">
         <v>0.06560000000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. IYOHA OSARENKHOE</t>
+          <t>A. GUIJARRO TOMAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.9232</v>
+        <v>-4.908</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.2167</v>
+        <v>-5.1867</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7070000000000001</v>
+        <v>0.2787</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.3158</v>
+        <v>-2.7878</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.8838</v>
+        <v>-2.7381</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4319</v>
+        <v>-0.04969999999999997</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.84</v>
+        <v>-2.9315</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.086600000000001</v>
+        <v>-1.6339</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2466</v>
+        <v>-1.2976</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4759</v>
+        <v>0.1436999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7974</v>
+        <v>-1.1041</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6782999999999998</v>
+        <v>1.2479</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5793999999999999</v>
+        <v>-1.1584</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.109400000000001</v>
+        <v>-1.9308</v>
       </c>
       <c r="R14" t="n">
-        <v>8.688700000000001</v>
+        <v>0.7724</v>
       </c>
       <c r="S14" t="n">
-        <v>5.1518</v>
+        <v>-1.0275</v>
       </c>
       <c r="T14" t="n">
-        <v>7.4166</v>
+        <v>-0.3244</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.2647</v>
+        <v>-0.7031000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.3388</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.6839</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.6549</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.1273</v>
+        <v>-6.965900000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.4773</v>
+        <v>-8.835700000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3499000000000002</v>
+        <v>1.87</v>
       </c>
       <c r="G15" t="n">
         <v>-1.0458</v>
@@ -1624,13 +1624,13 @@
         <v>5.985300000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.0784</v>
+        <v>-1.9169</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1365000000000001</v>
+        <v>-0.2218000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.215</v>
+        <v>-1.695</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9140000000000001</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-8.705099999999998</v>
+        <v>-9.1532</v>
       </c>
       <c r="E16" t="n">
-        <v>-13.3344</v>
+        <v>-17.8568</v>
       </c>
       <c r="F16" t="n">
-        <v>4.629200000000001</v>
+        <v>8.7037</v>
       </c>
       <c r="G16" t="n">
         <v>-16.4746</v>
@@ -1702,13 +1702,13 @@
         <v>30.5063</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.848199999999999</v>
+        <v>-3.2967</v>
       </c>
       <c r="T16" t="n">
-        <v>5.0392</v>
+        <v>0.5164000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-7.8872</v>
+        <v>-3.8129</v>
       </c>
       <c r="V16" t="n">
         <v>-3.4766</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>P. GRANJA I BERNAD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>-9.481200000000001</v>
+        <v>-9.320399999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-12.2797</v>
+        <v>-12.7453</v>
       </c>
       <c r="F17" t="n">
-        <v>2.798499999999999</v>
+        <v>3.424799999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.495299999999999</v>
+        <v>6.665</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.935</v>
+        <v>8.977</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.5604</v>
+        <v>-2.3121</v>
       </c>
       <c r="J17" t="n">
-        <v>19.9107</v>
+        <v>11.3781</v>
       </c>
       <c r="K17" t="n">
-        <v>14.7444</v>
+        <v>12.7809</v>
       </c>
       <c r="L17" t="n">
-        <v>5.166300000000001</v>
+        <v>-1.402599999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-25.4062</v>
+        <v>-4.7135</v>
       </c>
       <c r="N17" t="n">
-        <v>-17.6795</v>
+        <v>-3.803799999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.7266</v>
+        <v>-0.9094999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>22.59</v>
+        <v>-0.3860999999999996</v>
       </c>
       <c r="Q17" t="n">
-        <v>-34.3683</v>
+        <v>-25.4865</v>
       </c>
       <c r="R17" t="n">
-        <v>56.9578</v>
+        <v>25.1001</v>
       </c>
       <c r="S17" t="n">
-        <v>-27.5846</v>
+        <v>-4.8406</v>
       </c>
       <c r="T17" t="n">
-        <v>-20.8078</v>
+        <v>-2.7632</v>
       </c>
       <c r="U17" t="n">
-        <v>-6.7764</v>
+        <v>-2.0772</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0085</v>
+        <v>-10.7585</v>
       </c>
       <c r="W17" t="n">
-        <v>22.985</v>
+        <v>4.1264</v>
       </c>
       <c r="X17" t="n">
-        <v>-21.9763</v>
+        <v>-14.885</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>-10.379</v>
+        <v>-9.3858</v>
       </c>
       <c r="E18" t="n">
-        <v>-8.6699</v>
+        <v>-8.0495</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.709</v>
+        <v>-1.3364</v>
       </c>
       <c r="G18" t="n">
         <v>-2.9021</v>
@@ -1858,13 +1858,13 @@
         <v>2.8963</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.7858</v>
+        <v>-1.7929</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.0142</v>
+        <v>-1.3936</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7715000000000001</v>
+        <v>-0.3991</v>
       </c>
       <c r="V18" t="n">
         <v>-3.7257</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. GRANJA I BERNAD</t>
+          <t>D. IYOHA OSARENKHOE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>-17.626</v>
+        <v>-10.6755</v>
       </c>
       <c r="E19" t="n">
-        <v>-16.0271</v>
+        <v>-11.0221</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5988</v>
+        <v>0.3464</v>
       </c>
       <c r="G19" t="n">
-        <v>6.665</v>
+        <v>-6.3158</v>
       </c>
       <c r="H19" t="n">
-        <v>8.977</v>
+        <v>-5.8838</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.3121</v>
+        <v>-0.4319</v>
       </c>
       <c r="J19" t="n">
-        <v>11.3781</v>
+        <v>-3.84</v>
       </c>
       <c r="K19" t="n">
-        <v>12.7809</v>
+        <v>-4.086600000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.402599999999999</v>
+        <v>0.2466</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.7135</v>
+        <v>-2.4759</v>
       </c>
       <c r="N19" t="n">
-        <v>-3.803799999999999</v>
+        <v>-1.7974</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9094999999999999</v>
+        <v>-0.6782999999999998</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3860999999999996</v>
+        <v>0.5793999999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-25.4865</v>
+        <v>-8.109400000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>25.1001</v>
+        <v>8.688700000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>-13.1465</v>
+        <v>1.3997</v>
       </c>
       <c r="T19" t="n">
-        <v>-6.045100000000001</v>
+        <v>2.6111</v>
       </c>
       <c r="U19" t="n">
-        <v>-7.1009</v>
+        <v>-1.2113</v>
       </c>
       <c r="V19" t="n">
-        <v>-10.7585</v>
+        <v>-6.3388</v>
       </c>
       <c r="W19" t="n">
-        <v>4.1264</v>
+        <v>-1.6839</v>
       </c>
       <c r="X19" t="n">
-        <v>-14.885</v>
+        <v>-4.6549</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>-18.2621</v>
+        <v>-18.5405</v>
       </c>
       <c r="E20" t="n">
-        <v>-22.3998</v>
+        <v>-25.8882</v>
       </c>
       <c r="F20" t="n">
-        <v>4.1379</v>
+        <v>7.348</v>
       </c>
       <c r="G20" t="n">
         <v>3.090399999999999</v>
@@ -2014,13 +2014,13 @@
         <v>42.091</v>
       </c>
       <c r="S20" t="n">
-        <v>-5.4443</v>
+        <v>-5.7225</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3147</v>
+        <v>-2.1738</v>
       </c>
       <c r="U20" t="n">
-        <v>-6.7588</v>
+        <v>-3.5485</v>
       </c>
       <c r="V20" t="n">
         <v>-20.7353</v>
@@ -2047,13 +2047,13 @@
         <v>23</v>
       </c>
       <c r="D21" t="n">
-        <v>-20.2911</v>
+        <v>-19.2212</v>
       </c>
       <c r="E21" t="n">
-        <v>-19.4823</v>
+        <v>-19.7444</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.808399999999999</v>
+        <v>0.5229999999999994</v>
       </c>
       <c r="G21" t="n">
         <v>15.8416</v>
@@ -2092,13 +2092,13 @@
         <v>44.6011</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3726</v>
+        <v>-0.3030000000000002</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5613999999999999</v>
+        <v>-0.8229</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8115000000000001</v>
+        <v>0.5199000000000003</v>
       </c>
       <c r="V21" t="n">
         <v>-3.0948</v>
@@ -2125,19 +2125,19 @@
         <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>-22.45399999999999</v>
+        <v>9.229999999999979</v>
       </c>
       <c r="E22" t="n">
-        <v>-66.86649999999999</v>
+        <v>-60.693</v>
       </c>
       <c r="F22" t="n">
-        <v>44.41220000000001</v>
+        <v>69.9235</v>
       </c>
       <c r="G22" t="n">
         <v>68.25710000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>73.083</v>
+        <v>73.08300000000001</v>
       </c>
       <c r="I22" t="n">
         <v>-4.825799999999999</v>
@@ -2161,7 +2161,7 @@
         <v>-50.4941</v>
       </c>
       <c r="P22" t="n">
-        <v>17.37740000000001</v>
+        <v>17.3774</v>
       </c>
       <c r="Q22" t="n">
         <v>-404.5015</v>
@@ -2170,16 +2170,16 @@
         <v>421.8755</v>
       </c>
       <c r="S22" t="n">
-        <v>-93.77369999999999</v>
+        <v>-62.0894</v>
       </c>
       <c r="T22" t="n">
-        <v>-40.2251</v>
+        <v>-34.0513</v>
       </c>
       <c r="U22" t="n">
-        <v>-53.54780000000001</v>
+        <v>-28.0369</v>
       </c>
       <c r="V22" t="n">
-        <v>-14.3147</v>
+        <v>-14.31469999999999</v>
       </c>
       <c r="W22" t="n">
         <v>145.1357</v>
